--- a/ig/DM-37/CodeSystem-TRE-R344-NiveauExpertise.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-R344-NiveauExpertise.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="100">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -308,6 +308,12 @@
   </si>
   <si>
     <t>Filière endométriose - troisième niveau de recours</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Centre labellisé Covid-Long</t>
   </si>
 </sst>
 </file>
@@ -681,7 +687,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -986,6 +992,18 @@
       </c>
       <c r="D25" s="2"/>
     </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="D26" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
